--- a/astro-site/public/dl/haccp-templates/07-pest-control-log.xlsx
+++ b/astro-site/public/dl/haccp-templates/07-pest-control-log.xlsx
@@ -678,7 +678,7 @@
     <row r="6">
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>▸ Record ALL actions: insect treatment, rodent treatment, disinfection, bait station checks and your own visual inspections. The sheet has 80 rows, which is enough for a full year.</t>
+          <t>▸ Record ALL actions: insect treatment, rodent treatment, exclusion / proofing checks, bait station checks and your own visual inspections. The sheet has 80 rows, which is enough for a full year.</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
     <row r="15">
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>▸ General disinfection: twice a year.</t>
+          <t>▸ Exclusion / proofing check (door sweeps, gaps, screens and drains): twice a year, and after any building work.</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1998,7 @@
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="B5:B84" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Type of treatment" error="Pick a treatment from the list." type="list" errorStyle="stop">
-      <formula1>"Insect treatment,Rodent treatment,Disinfection,Bait station check,Visual inspection,Other"</formula1>
+      <formula1>"Insect treatment,Rodent treatment,Exclusion / proofing check,Bait station check,Visual inspection,Other"</formula1>
     </dataValidation>
     <dataValidation sqref="F5:F84" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Re-entry interval" error="Enter the re-entry interval in hours, between 0 and 168. It is on the pesticide label; until it has passed, food cannot be handled in the treated area." type="decimal" errorStyle="stop" operator="between">
       <formula1>0</formula1>
